--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.96736891608091</v>
+        <v>12.34469744886315</v>
       </c>
       <c r="D2" t="n">
-        <v>74.36145035665523</v>
+        <v>12.08373568295647</v>
       </c>
       <c r="E2" t="n">
-        <v>4.044817941829372</v>
+        <v>0.657282915547273</v>
       </c>
       <c r="F2" t="n">
-        <v>3.285806400309525</v>
+        <v>0.5339435400502976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.87773303242217</v>
+        <v>11.0301316177686</v>
       </c>
       <c r="D3" t="n">
-        <v>67.78983755603618</v>
+        <v>11.01584860285588</v>
       </c>
       <c r="E3" t="n">
-        <v>4.044817941829372</v>
+        <v>0.657282915547273</v>
       </c>
       <c r="F3" t="n">
-        <v>3.285806400309525</v>
+        <v>0.5339435400502976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
